--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령.jpg.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령.jpg.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I20" s="2"/>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I31" s="2"/>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I32" s="2"/>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I41" s="2"/>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -2523,12 +2523,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I60" s="2"/>
@@ -3681,12 +3681,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P3" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -5171,7 +5171,7 @@
       <c r="Q5" s="10"/>
       <c r="R5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K6" s="8"/>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O11" s="10"/>
@@ -5892,13 +5892,13 @@
       </c>
       <c r="P13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S13" s="9"/>
@@ -5960,7 +5960,7 @@
       <c r="O14" s="10"/>
       <c r="P14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q14" s="10"/>

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령.jpg.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령.jpg.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4870,126 +4911,126 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">창부타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙
 姑</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">공</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙
 仲</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">알</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">민</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="18" t="inlineStr">
+      <c r="Q3" s="24"/>
+      <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙
 仲</t>
         </is>
       </c>
-      <c r="S3" s="11"/>
-      <c r="T3" s="17" t="inlineStr">
+      <c r="S3" s="22"/>
+      <c r="T3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="U3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4997,102 +5038,102 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">깍</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="R4" s="18" t="inlineStr">
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="S4" s="12" t="inlineStr">
+      <c r="S4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="T4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U4" s="9" t="inlineStr">
+      <c r="T4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -5100,426 +5141,426 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="E5" s="27"/>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">딸</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="I5" s="27"/>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="Q5" s="27"/>
+      <c r="R5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="S5" s="10"/>
-      <c r="T5" s="17"/>
-      <c r="U5" s="10"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="27"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="B6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="24"/>
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">조</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="K6" s="24"/>
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">란</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="R6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="R6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="T6" s="17"/>
-      <c r="U6" s="8"/>
+      <c r="T6" s="23"/>
+      <c r="U6" s="24"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">카아</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr">
+      <c r="K7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">조</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">도오</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">것</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="R7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="S7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="T7" s="17"/>
-      <c r="U7" s="9"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="25"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="B8" s="23"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아악</t>
         </is>
       </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="H8" s="23"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="27"/>
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">오오</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="P8" s="23"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="T8" s="17"/>
-      <c r="U8" s="10"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="27"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">깊</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">싸아</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">소은</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">모호</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="R9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
+      <c r="S9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="T9" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U9" s="11" t="inlineStr">
+      <c r="T9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5527,300 +5568,300 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">밝던</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">우우은</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">우은</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">뜨을</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">으은</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">엇</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="R10" s="18" t="inlineStr">
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="S10" s="12" t="inlineStr">
+      <c r="S10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="T10" s="17" t="inlineStr">
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="U10" s="9"/>
+      <c r="U10" s="25"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">우은</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="27"/>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">으을</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">흘</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="O11" s="27"/>
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="Q11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이러</t>
         </is>
       </c>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="R11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="T11" s="17" t="inlineStr">
+      <c r="T11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="U11" s="10"/>
+      <c r="U11" s="27"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="J12" s="18" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="R12" s="18" t="inlineStr">
+      <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="S12" s="11" t="inlineStr">
+      <c r="S12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="T12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
+      <c r="T12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5828,155 +5869,155 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에에</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라아</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라앙</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라앙</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="N13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="Q13" s="25"/>
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S13" s="9"/>
-      <c r="T13" s="17" t="inlineStr">
+      <c r="S13" s="25"/>
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="U13" s="9"/>
+      <c r="U13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="27"/>
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="27"/>
+      <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="27"/>
+      <c r="P14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="17" t="inlineStr">
+      <c r="Q14" s="27"/>
+      <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S14" s="10"/>
-      <c r="T14" s="17" t="inlineStr">
+      <c r="S14" s="27"/>
+      <c r="T14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="U14" s="10"/>
+      <c r="U14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령.jpg.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령.jpg.xlsx
@@ -4884,32 +4884,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E5" s="27"/>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="27"/>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="P5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q5" s="27"/>
@@ -5220,7 +5220,7 @@
       <c r="T5" s="23"/>
       <c r="U5" s="27"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23"/>
       <c r="C6" s="24"/>
@@ -5301,7 +5301,7 @@
       <c r="T6" s="23"/>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
       <c r="T7" s="23"/>
       <c r="U7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23"/>
       <c r="C8" s="27"/>
@@ -5459,7 +5459,7 @@
       <c r="T8" s="23"/>
       <c r="U8" s="27"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="U10" s="25"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="U11" s="27"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G13" s="25"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="J13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="25"/>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
       <c r="E14" s="27"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="27"/>
@@ -5983,7 +5983,7 @@
       <c r="I14" s="27"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="27"/>
@@ -5995,7 +5995,7 @@
       <c r="M14" s="27"/>
       <c r="N14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O14" s="27"/>
@@ -6007,7 +6007,7 @@
       <c r="Q14" s="27"/>
       <c r="R14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S14" s="27"/>

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령.jpg.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령.jpg.xlsx
@@ -5330,7 +5330,8 @@
       </c>
       <c r="G7" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">카아</t>
+          <t xml:space="preserve">카
+아</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
@@ -5361,7 +5362,8 @@
       </c>
       <c r="M7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">도오</t>
+          <t xml:space="preserve">도
+오</t>
         </is>
       </c>
       <c r="N7" s="23" t="inlineStr">
@@ -5411,7 +5413,8 @@
       </c>
       <c r="G8" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">아악</t>
+          <t xml:space="preserve">아
+악</t>
         </is>
       </c>
       <c r="H8" s="23"/>
@@ -5430,7 +5433,8 @@
       </c>
       <c r="M8" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">오오</t>
+          <t xml:space="preserve">오
+오</t>
         </is>
       </c>
       <c r="N8" s="23" t="inlineStr">
@@ -5488,7 +5492,8 @@
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">싸아</t>
+          <t xml:space="preserve">싸
+아</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
@@ -5509,7 +5514,8 @@
       </c>
       <c r="K9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">소은</t>
+          <t xml:space="preserve">소
+은</t>
         </is>
       </c>
       <c r="L9" s="23" t="inlineStr">
@@ -5520,7 +5526,8 @@
       </c>
       <c r="M9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">모호</t>
+          <t xml:space="preserve">모
+호</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
@@ -5576,7 +5583,8 @@
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">밝던</t>
+          <t xml:space="preserve">밝
+던</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -5586,7 +5594,9 @@
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">우우은</t>
+          <t xml:space="preserve">우
+우
+은</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -5597,7 +5607,8 @@
       </c>
       <c r="G10" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">우은</t>
+          <t xml:space="preserve">우
+은</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -5608,7 +5619,8 @@
       </c>
       <c r="I10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">뜨을</t>
+          <t xml:space="preserve">뜨
+을</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -5619,7 +5631,8 @@
       </c>
       <c r="K10" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">으은</t>
+          <t xml:space="preserve">으
+은</t>
         </is>
       </c>
       <c r="L10" s="23" t="inlineStr">
@@ -5680,7 +5693,8 @@
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">우은</t>
+          <t xml:space="preserve">우
+은</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -5706,7 +5720,8 @@
       </c>
       <c r="I11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">으을</t>
+          <t xml:space="preserve">으
+을</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -5743,7 +5758,8 @@
       </c>
       <c r="Q11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">이러</t>
+          <t xml:space="preserve">이
+러</t>
         </is>
       </c>
       <c r="R11" s="23" t="inlineStr">
@@ -5876,7 +5892,8 @@
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">에에</t>
+          <t xml:space="preserve">에
+에</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -5886,7 +5903,8 @@
       </c>
       <c r="E13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">라아</t>
+          <t xml:space="preserve">라
+아</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -5902,7 +5920,8 @@
       </c>
       <c r="I13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">라앙</t>
+          <t xml:space="preserve">라
+앙</t>
         </is>
       </c>
       <c r="J13" s="23" t="inlineStr">
@@ -5918,7 +5937,8 @@
       </c>
       <c r="M13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">라앙</t>
+          <t xml:space="preserve">라
+앙</t>
         </is>
       </c>
       <c r="N13" s="23" t="inlineStr">

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령.jpg.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령.jpg.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4944,7 +4967,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">공</t>
         </is>
@@ -4955,7 +4978,7 @@
 仲</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -4965,7 +4988,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">알</t>
         </is>
@@ -4975,7 +4998,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -4985,7 +5008,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">민</t>
         </is>
@@ -4995,7 +5018,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -5006,7 +5029,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O3" s="24" t="inlineStr">
+      <c r="O3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5017,20 +5040,20 @@
 汰</t>
         </is>
       </c>
-      <c r="Q3" s="24"/>
+      <c r="Q3" s="30"/>
       <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙
 仲</t>
         </is>
       </c>
-      <c r="S3" s="22"/>
+      <c r="S3" s="29"/>
       <c r="T3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="U3" s="24" t="inlineStr">
+      <c r="U3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5043,7 +5066,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -5053,7 +5076,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
@@ -5063,7 +5086,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">깍</t>
         </is>
@@ -5073,7 +5096,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
@@ -5083,7 +5106,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5093,7 +5116,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5103,7 +5126,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -5113,7 +5136,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="Q4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -5123,7 +5146,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="S4" s="26" t="inlineStr">
+      <c r="S4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -5133,7 +5156,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U4" s="25" t="inlineStr">
+      <c r="U4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -5146,7 +5169,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5156,13 +5179,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="33"/>
       <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">딸</t>
         </is>
@@ -5172,13 +5195,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="27"/>
+      <c r="I5" s="33"/>
       <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5189,7 +5212,7 @@
 無</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="M5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5199,7 +5222,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
+      <c r="O5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5209,27 +5232,27 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q5" s="27"/>
+      <c r="Q5" s="33"/>
       <c r="R5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="S5" s="27"/>
+      <c r="S5" s="33"/>
       <c r="T5" s="23"/>
-      <c r="U5" s="27"/>
+      <c r="U5" s="33"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23"/>
-      <c r="C6" s="24"/>
+      <c r="C6" s="30"/>
       <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -5240,13 +5263,13 @@
 △</t>
         </is>
       </c>
-      <c r="G6" s="24"/>
+      <c r="G6" s="30"/>
       <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">조</t>
         </is>
@@ -5256,14 +5279,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="24"/>
+      <c r="K6" s="30"/>
       <c r="L6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="M6" s="24" t="inlineStr">
+      <c r="M6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5273,7 +5296,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="O6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">란</t>
         </is>
@@ -5283,7 +5306,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q6" s="24" t="inlineStr">
+      <c r="Q6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5293,13 +5316,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S6" s="24" t="inlineStr">
+      <c r="S6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
       <c r="T6" s="23"/>
-      <c r="U6" s="24"/>
+      <c r="U6" s="30"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -5308,7 +5331,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
@@ -5318,7 +5341,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
@@ -5328,7 +5351,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">카
 아</t>
@@ -5339,7 +5362,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
@@ -5349,7 +5372,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="K7" s="26" t="inlineStr">
+      <c r="K7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">조</t>
         </is>
@@ -5360,7 +5383,7 @@
 汰</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">도
 오</t>
@@ -5372,7 +5395,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">것</t>
         </is>
@@ -5382,7 +5405,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="Q7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -5392,46 +5415,46 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="S7" s="25" t="inlineStr">
+      <c r="S7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
       <c r="T7" s="23"/>
-      <c r="U7" s="25"/>
+      <c r="U7" s="31"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="27"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="23"/>
-      <c r="E8" s="27"/>
+      <c r="E8" s="33"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 악</t>
         </is>
       </c>
       <c r="H8" s="23"/>
-      <c r="I8" s="27"/>
+      <c r="I8" s="33"/>
       <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="K8" s="27"/>
+      <c r="K8" s="33"/>
       <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="M8" s="27" t="inlineStr">
+      <c r="M8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">오
 오</t>
@@ -5443,25 +5466,25 @@
 潢</t>
         </is>
       </c>
-      <c r="O8" s="27" t="inlineStr">
+      <c r="O8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="P8" s="23"/>
-      <c r="Q8" s="27"/>
+      <c r="Q8" s="33"/>
       <c r="R8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="S8" s="27" t="inlineStr">
+      <c r="S8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
       <c r="T8" s="23"/>
-      <c r="U8" s="27"/>
+      <c r="U8" s="33"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -5470,7 +5493,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
@@ -5480,7 +5503,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">깊</t>
         </is>
@@ -5490,7 +5513,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">싸
 아</t>
@@ -5502,7 +5525,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -5512,7 +5535,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="K9" s="24" t="inlineStr">
+      <c r="K9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">소
 은</t>
@@ -5524,7 +5547,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M9" s="24" t="inlineStr">
+      <c r="M9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">모
 호</t>
@@ -5536,7 +5559,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O9" s="24" t="inlineStr">
+      <c r="O9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -5547,7 +5570,7 @@
 汰</t>
         </is>
       </c>
-      <c r="Q9" s="24" t="inlineStr">
+      <c r="Q9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5557,7 +5580,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="S9" s="24" t="inlineStr">
+      <c r="S9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
@@ -5567,7 +5590,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U9" s="22" t="inlineStr">
+      <c r="U9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5581,7 +5604,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">밝
 던</t>
@@ -5592,7 +5615,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 우
@@ -5605,7 +5628,7 @@
 僙</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 은</t>
@@ -5617,7 +5640,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">뜨
 을</t>
@@ -5629,7 +5652,7 @@
 僙</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">으
 은</t>
@@ -5640,7 +5663,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
@@ -5650,7 +5673,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">엇</t>
         </is>
@@ -5661,7 +5684,7 @@
 潢</t>
         </is>
       </c>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="Q10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -5672,7 +5695,7 @@
 僙</t>
         </is>
       </c>
-      <c r="S10" s="26" t="inlineStr">
+      <c r="S10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -5682,7 +5705,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="U10" s="25"/>
+      <c r="U10" s="31"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -5691,7 +5714,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 은</t>
@@ -5702,13 +5725,13 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="E11" s="27"/>
+      <c r="E11" s="33"/>
       <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G11" s="27" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5718,7 +5741,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">으
 을</t>
@@ -5729,7 +5752,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K11" s="27" t="inlineStr">
+      <c r="K11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5740,7 +5763,7 @@
 無</t>
         </is>
       </c>
-      <c r="M11" s="27" t="inlineStr">
+      <c r="M11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">흘</t>
         </is>
@@ -5750,13 +5773,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O11" s="27"/>
+      <c r="O11" s="33"/>
       <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="Q11" s="27" t="inlineStr">
+      <c r="Q11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 러</t>
@@ -5767,7 +5790,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S11" s="27" t="inlineStr">
+      <c r="S11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -5777,7 +5800,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="U11" s="27"/>
+      <c r="U11" s="33"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -5786,7 +5809,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
@@ -5796,7 +5819,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5806,7 +5829,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -5816,7 +5839,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5826,7 +5849,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -5836,7 +5859,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M12" s="24" t="inlineStr">
+      <c r="M12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5846,7 +5869,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O12" s="24" t="inlineStr">
+      <c r="O12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5857,7 +5880,7 @@
 潢</t>
         </is>
       </c>
-      <c r="Q12" s="24" t="inlineStr">
+      <c r="Q12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -5867,7 +5890,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="S12" s="22" t="inlineStr">
+      <c r="S12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -5877,7 +5900,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U12" s="24" t="inlineStr">
+      <c r="U12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5890,7 +5913,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에
 에</t>
@@ -5901,7 +5924,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">라
 아</t>
@@ -5912,13 +5935,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">라
 앙</t>
@@ -5929,13 +5952,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">라
 앙</t>
@@ -5946,7 +5969,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O13" s="25" t="inlineStr">
+      <c r="O13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -5956,19 +5979,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="31"/>
       <c r="R13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S13" s="25"/>
+      <c r="S13" s="31"/>
       <c r="T13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="U13" s="25"/>
+      <c r="U13" s="31"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -5978,7 +6001,7 @@
 僙</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5988,56 +6011,56 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I14" s="27"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M14" s="27"/>
+      <c r="M14" s="33"/>
       <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O14" s="27"/>
+      <c r="O14" s="33"/>
       <c r="P14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="27"/>
+      <c r="Q14" s="33"/>
       <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S14" s="27"/>
+      <c r="S14" s="33"/>
       <c r="T14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="U14" s="27"/>
+      <c r="U14" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령.jpg.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령.jpg.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,12 +212,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -232,31 +221,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -357,7 +334,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">111</t>
+          <t xml:space="preserve">114</t>
         </is>
       </c>
     </row>
@@ -369,7 +346,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
     </row>
@@ -429,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12. 제목 "창부타령 1 굿거리", 오른쪽 위 "C#키"·"1절". 오른쪽부터 1줄, 10줄 사용. 가사는 각 율명 줄 오른쪽 좁은 칸의 음절. 亻黃(배황종)은 僙으로 적음. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 한 줄 12정간(굵은 선 3칸마다) → 3/4·12. 제목 "창부타령 1 굿거리", 오른쪽 위 "C#키"·"1절". 오른쪽부터 10줄, 가사는 각 율명 줄 오른쪽 좁은 칸. 흘림 南(十+冂)·姑(女古)를 구별, 氵仲(神 모양)=㳞, 氵姑=㴌, 氵南=湳. 한 칸에 위아래로 쌓인 두 글자는 |로 구분. 줄1은 시작 '아아니'와 각 장 끝 '이' 받침 가락. 한 곡.</t>
         </is>
       </c>
     </row>
@@ -617,17 +594,18 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">姑|仲</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">姑
+仲</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아</t>
+          <t xml:space="preserve">아아</t>
         </is>
       </c>
       <c r="J2" s="4"/>
@@ -656,12 +634,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -688,29 +666,25 @@
         <v>1</v>
       </c>
       <c r="E4" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I4" s="3"/>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞에 경계 ‹ 표시</t>
+          <t xml:space="preserve">오른쪽 경계에 &lt; 표시</t>
         </is>
       </c>
       <c r="K4" s="2"/>
@@ -731,22 +705,26 @@
         <v>1</v>
       </c>
       <c r="E5" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
         <v>3</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
       <c r="J5" s="4"/>
       <c r="K5" s="2"/>
     </row>
@@ -766,19 +744,20 @@
         <v>1</v>
       </c>
       <c r="E6" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I6" s="2"/>
@@ -801,26 +780,23 @@
         <v>1</v>
       </c>
       <c r="E7" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I7" s="2"/>
       <c r="J7" s="4"/>
       <c r="K7" s="2"/>
     </row>
@@ -840,22 +816,26 @@
         <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2">
         <v>4</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
       <c r="J8" s="4"/>
       <c r="K8" s="2"/>
     </row>
@@ -875,20 +855,20 @@
         <v>1</v>
       </c>
       <c r="E9" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="2">
         <v>4</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|僙</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-僙</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -905,34 +885,30 @@
         </is>
       </c>
       <c r="C10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙|仲</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙
-仲</t>
-        </is>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="4"/>
       <c r="K10" s="2"/>
     </row>
     <row r="11">
@@ -951,31 +927,27 @@
         <v>2</v>
       </c>
       <c r="E11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
     <row r="12">
@@ -994,62 +966,62 @@
         <v>2</v>
       </c>
       <c r="E12" s="2">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니</t>
+        </is>
+      </c>
+      <c r="J12" s="4"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령.jpg</t>
+        </is>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
         <v>3</v>
       </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–|仲</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2">
-        <v>1</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령.jpg</t>
-        </is>
-      </c>
-      <c r="C13" s="2">
-        <v>2</v>
-      </c>
-      <c r="D13" s="2">
-        <v>2</v>
-      </c>
-      <c r="E13" s="2">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2">
-        <v>2</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">놀</t>
-        </is>
-      </c>
+      <c r="I13" s="2"/>
       <c r="J13" s="4"/>
       <c r="K13" s="2"/>
     </row>
@@ -1069,24 +1041,24 @@
         <v>2</v>
       </c>
       <c r="E14" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="2">
         <v>2</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">지</t>
+          <t xml:space="preserve">놀</t>
         </is>
       </c>
       <c r="J14" s="4"/>
@@ -1108,24 +1080,25 @@
         <v>2</v>
       </c>
       <c r="E15" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" s="2">
         <v>2</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">는</t>
+          <t xml:space="preserve">지</t>
         </is>
       </c>
       <c r="J15" s="4"/>
@@ -1147,24 +1120,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+潢</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">못</t>
+          <t xml:space="preserve">는</t>
         </is>
       </c>
       <c r="J16" s="4"/>
@@ -1186,32 +1160,28 @@
         <v>2</v>
       </c>
       <c r="E17" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" s="2">
         <v>3</v>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">못</t>
+        </is>
+      </c>
+      <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
     <row r="18">
@@ -1230,24 +1200,25 @@
         <v>2</v>
       </c>
       <c r="E18" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" s="2">
         <v>3</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲
+姑</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">리</t>
+          <t xml:space="preserve">하</t>
         </is>
       </c>
       <c r="J18" s="4"/>
@@ -1269,31 +1240,27 @@
         <v>2</v>
       </c>
       <c r="E19" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" s="2">
-        <v>4</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">라</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
+      <c r="J19" s="4"/>
       <c r="K19" s="2"/>
     </row>
     <row r="20">
@@ -1312,22 +1279,26 @@
         <v>2</v>
       </c>
       <c r="E20" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F20" s="2">
         <v>4</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I20" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라</t>
+        </is>
+      </c>
       <c r="J20" s="4"/>
       <c r="K20" s="2"/>
     </row>
@@ -1347,19 +1318,19 @@
         <v>2</v>
       </c>
       <c r="E21" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="2">
         <v>4</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I21" s="2"/>
@@ -1376,26 +1347,26 @@
         </is>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F22" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|汰</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰</t>
+△</t>
         </is>
       </c>
       <c r="I22" s="2"/>
@@ -1418,24 +1389,25 @@
         <v>3</v>
       </c>
       <c r="E23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌|–湳</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌
+–湳</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">랑</t>
+          <t xml:space="preserve">사</t>
         </is>
       </c>
       <c r="J23" s="4"/>
@@ -1457,22 +1429,26 @@
         <v>3</v>
       </c>
       <c r="E24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" s="2">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I24" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
       <c r="J24" s="4"/>
       <c r="K24" s="2"/>
     </row>
@@ -1492,27 +1468,27 @@
         <v>3</v>
       </c>
       <c r="E25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" s="2">
-        <v>2</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
-      <c r="J25" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작은 사선(、) — –로 봄</t>
+        </is>
+      </c>
       <c r="K25" s="2"/>
     </row>
     <row r="26">
@@ -1531,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" s="2">
         <v>2</v>
@@ -1548,7 +1524,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">랑</t>
+          <t xml:space="preserve">사</t>
         </is>
       </c>
       <c r="J26" s="4"/>
@@ -1570,25 +1546,24 @@
         <v>3</v>
       </c>
       <c r="E27" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F27" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-汰</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사</t>
+          <t xml:space="preserve">랑</t>
         </is>
       </c>
       <c r="J27" s="4"/>
@@ -1610,25 +1585,25 @@
         <v>3</v>
       </c>
       <c r="E28" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F28" s="2">
         <v>3</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|湳</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+湳</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">랑</t>
+          <t xml:space="preserve">사</t>
         </is>
       </c>
       <c r="J28" s="4"/>
@@ -1650,24 +1625,25 @@
         <v>3</v>
       </c>
       <c r="E29" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" s="2">
         <v>3</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">㳞
+㴌</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이러</t>
+          <t xml:space="preserve">랑</t>
         </is>
       </c>
       <c r="J29" s="4"/>
@@ -1689,25 +1665,25 @@
         <v>3</v>
       </c>
       <c r="E30" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F30" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">니</t>
+          <t xml:space="preserve">이러</t>
         </is>
       </c>
       <c r="J30" s="4"/>
@@ -1729,22 +1705,26 @@
         <v>3</v>
       </c>
       <c r="E31" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F31" s="2">
         <v>4</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I31" s="2"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니</t>
+        </is>
+      </c>
       <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
@@ -1764,7 +1744,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F32" s="2">
         <v>4</v>
@@ -1793,33 +1773,29 @@
         </is>
       </c>
       <c r="C33" s="2">
+        <v>3</v>
+      </c>
+      <c r="D33" s="2">
+        <v>3</v>
+      </c>
+      <c r="E33" s="2">
+        <v>12</v>
+      </c>
+      <c r="F33" s="2">
         <v>4</v>
       </c>
-      <c r="D33" s="2">
-        <v>4</v>
-      </c>
-      <c r="E33" s="2">
-        <v>1</v>
-      </c>
-      <c r="F33" s="2">
-        <v>1</v>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I33" s="2"/>
       <c r="J33" s="4"/>
       <c r="K33" s="2"/>
     </row>
@@ -1839,24 +1815,25 @@
         <v>4</v>
       </c>
       <c r="E34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㳞
+㴌</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">랑</t>
+          <t xml:space="preserve">사</t>
         </is>
       </c>
       <c r="J34" s="4"/>
@@ -1878,24 +1855,24 @@
         <v>4</v>
       </c>
       <c r="E35" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" s="2">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">랑</t>
         </is>
       </c>
       <c r="J35" s="4"/>
@@ -1917,24 +1894,24 @@
         <v>4</v>
       </c>
       <c r="E36" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">란</t>
+          <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="J36" s="4"/>
@@ -1956,28 +1933,31 @@
         <v>4</v>
       </c>
       <c r="E37" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F37" s="2">
         <v>2</v>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞|潢</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">것</t>
-        </is>
-      </c>
-      <c r="J37" s="4"/>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">란</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 란/관?</t>
+        </is>
+      </c>
       <c r="K37" s="2"/>
     </row>
     <row r="38">
@@ -1996,25 +1976,25 @@
         <v>4</v>
       </c>
       <c r="E38" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F38" s="2">
         <v>2</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㴌|湳</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">㴌
+湳</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">것</t>
         </is>
       </c>
       <c r="J38" s="4"/>
@@ -2036,25 +2016,25 @@
         <v>4</v>
       </c>
       <c r="E39" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F39" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">무</t>
+          <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="J39" s="4"/>
@@ -2076,24 +2056,25 @@
         <v>4</v>
       </c>
       <c r="E40" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F40" s="2">
         <v>3</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㳞
+㴌</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">엇</t>
+          <t xml:space="preserve">무</t>
         </is>
       </c>
       <c r="J40" s="4"/>
@@ -2115,22 +2096,26 @@
         <v>4</v>
       </c>
       <c r="E41" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F41" s="2">
         <v>3</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I41" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">엇</t>
+        </is>
+      </c>
       <c r="J41" s="4"/>
       <c r="K41" s="2"/>
     </row>
@@ -2150,26 +2135,22 @@
         <v>4</v>
       </c>
       <c r="E42" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F42" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I42" s="2"/>
       <c r="J42" s="4"/>
       <c r="K42" s="2"/>
     </row>
@@ -2189,24 +2170,24 @@
         <v>4</v>
       </c>
       <c r="E43" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F43" s="2">
         <v>4</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">나</t>
+          <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="J43" s="4"/>
@@ -2228,23 +2209,31 @@
         <v>4</v>
       </c>
       <c r="E44" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F44" s="2">
         <v>4</v>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I44" s="2"/>
-      <c r="J44" s="4"/>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">냐</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 나/냐?</t>
+        </is>
+      </c>
       <c r="K44" s="2"/>
     </row>
     <row r="45">
@@ -2257,32 +2246,29 @@
         </is>
       </c>
       <c r="C45" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F45" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">얼</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I45" s="2"/>
       <c r="J45" s="4"/>
       <c r="K45" s="2"/>
     </row>
@@ -2302,24 +2288,24 @@
         <v>5</v>
       </c>
       <c r="E46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="2">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">다</t>
+          <t xml:space="preserve">얼</t>
         </is>
       </c>
       <c r="J46" s="4"/>
@@ -2341,65 +2327,64 @@
         <v>5</v>
       </c>
       <c r="E47" s="2">
+        <v>2</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="J47" s="4"/>
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>1</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령.jpg</t>
+        </is>
+      </c>
+      <c r="C48" s="2">
+        <v>5</v>
+      </c>
+      <c r="D48" s="2">
+        <v>5</v>
+      </c>
+      <c r="E48" s="2">
         <v>3</v>
       </c>
-      <c r="F47" s="2">
-        <v>1</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="F48" s="2">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–|無</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J47" s="4"/>
-      <c r="K47" s="2"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2">
-        <v>1</v>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령.jpg</t>
-        </is>
-      </c>
-      <c r="C48" s="2">
-        <v>5</v>
-      </c>
-      <c r="D48" s="2">
-        <v>5</v>
-      </c>
-      <c r="E48" s="2">
-        <v>4</v>
-      </c>
-      <c r="F48" s="2">
-        <v>2</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞|潢</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
         </is>
       </c>
       <c r="J48" s="4"/>
@@ -2421,25 +2406,24 @@
         <v>5</v>
       </c>
       <c r="E49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F49" s="2">
         <v>2</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">도오</t>
+          <t xml:space="preserve">가</t>
         </is>
       </c>
       <c r="J49" s="4"/>
@@ -2461,25 +2445,25 @@
         <v>5</v>
       </c>
       <c r="E50" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F50" s="2">
         <v>2</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㴌|湳</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">㴌
+湳</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오오</t>
+          <t xml:space="preserve">도오</t>
         </is>
       </c>
       <c r="J50" s="4"/>
@@ -2501,25 +2485,25 @@
         <v>5</v>
       </c>
       <c r="E51" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F51" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모호</t>
+          <t xml:space="preserve">오호</t>
         </is>
       </c>
       <c r="J51" s="4"/>
@@ -2541,24 +2525,25 @@
         <v>5</v>
       </c>
       <c r="E52" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F52" s="2">
         <v>3</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㳞
+㴌</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">를</t>
+          <t xml:space="preserve">모호</t>
         </is>
       </c>
       <c r="J52" s="4"/>
@@ -2580,64 +2565,64 @@
         <v>5</v>
       </c>
       <c r="E53" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F53" s="2">
         <v>3</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">를</t>
+        </is>
+      </c>
+      <c r="J53" s="4"/>
+      <c r="K53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>1</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령.jpg</t>
+        </is>
+      </c>
+      <c r="C54" s="2">
+        <v>5</v>
+      </c>
+      <c r="D54" s="2">
+        <v>5</v>
+      </c>
+      <c r="E54" s="2">
+        <v>9</v>
+      </c>
+      <c r="F54" s="2">
+        <v>3</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">–|無</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">흘</t>
-        </is>
-      </c>
-      <c r="J53" s="4"/>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2">
-        <v>1</v>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령.jpg</t>
-        </is>
-      </c>
-      <c r="C54" s="2">
-        <v>5</v>
-      </c>
-      <c r="D54" s="2">
-        <v>5</v>
-      </c>
-      <c r="E54" s="2">
-        <v>10</v>
-      </c>
-      <c r="F54" s="2">
-        <v>4</v>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
         </is>
       </c>
       <c r="J54" s="4"/>
@@ -2659,24 +2644,24 @@
         <v>5</v>
       </c>
       <c r="E55" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F55" s="2">
         <v>4</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">라앙</t>
+          <t xml:space="preserve">사</t>
         </is>
       </c>
       <c r="J55" s="4"/>
@@ -2698,22 +2683,27 @@
         <v>5</v>
       </c>
       <c r="E56" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F56" s="2">
         <v>4</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I56" s="2"/>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라앙</t>
+        </is>
+      </c>
       <c r="J56" s="4"/>
       <c r="K56" s="2"/>
     </row>
@@ -2727,33 +2717,34 @@
         </is>
       </c>
       <c r="C57" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D57" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E57" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F57" s="2">
-        <v>1</v>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민</t>
-        </is>
-      </c>
-      <c r="J57" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="I57" s="3"/>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 칸에 ㅣ(늘임)만</t>
+        </is>
+      </c>
       <c r="K57" s="2"/>
     </row>
     <row r="58">
@@ -2772,24 +2763,24 @@
         <v>6</v>
       </c>
       <c r="E58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58" s="2">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">다</t>
+          <t xml:space="preserve">민</t>
         </is>
       </c>
       <c r="J58" s="4"/>
@@ -2811,24 +2802,24 @@
         <v>6</v>
       </c>
       <c r="E59" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59" s="2">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가</t>
+          <t xml:space="preserve">다</t>
         </is>
       </c>
       <c r="J59" s="4"/>
@@ -2850,22 +2841,26 @@
         <v>6</v>
       </c>
       <c r="E60" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I60" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
       <c r="J60" s="4"/>
       <c r="K60" s="2"/>
     </row>
@@ -2885,31 +2880,23 @@
         <v>6</v>
       </c>
       <c r="E61" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F61" s="2">
         <v>2</v>
       </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조</t>
-        </is>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 조? 확실치 않음</t>
-        </is>
-      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I61" s="2"/>
+      <c r="J61" s="4"/>
       <c r="K61" s="2"/>
     </row>
     <row r="62">
@@ -2928,22 +2915,27 @@
         <v>6</v>
       </c>
       <c r="E62" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F62" s="2">
         <v>2</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="I62" s="2"/>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도오</t>
+        </is>
+      </c>
       <c r="J62" s="4"/>
       <c r="K62" s="2"/>
     </row>
@@ -2963,24 +2955,25 @@
         <v>6</v>
       </c>
       <c r="E63" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F63" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+潢</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소은</t>
+          <t xml:space="preserve">호오</t>
         </is>
       </c>
       <c r="J63" s="4"/>
@@ -3002,32 +2995,28 @@
         <v>6</v>
       </c>
       <c r="E64" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F64" s="2">
         <v>3</v>
       </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">으은</t>
-        </is>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소은</t>
+        </is>
+      </c>
+      <c r="J64" s="4"/>
       <c r="K64" s="2"/>
     </row>
     <row r="65">
@@ -3046,24 +3035,25 @@
         <v>6</v>
       </c>
       <c r="E65" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F65" s="2">
         <v>3</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲
+姑</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사</t>
+          <t xml:space="preserve">으은</t>
         </is>
       </c>
       <c r="J65" s="4"/>
@@ -3085,31 +3075,27 @@
         <v>6</v>
       </c>
       <c r="E66" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F66" s="2">
-        <v>4</v>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+      <c r="J66" s="4"/>
       <c r="K66" s="2"/>
     </row>
     <row r="67">
@@ -3128,22 +3114,26 @@
         <v>6</v>
       </c>
       <c r="E67" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F67" s="2">
         <v>4</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I67" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
       <c r="J67" s="4"/>
       <c r="K67" s="2"/>
     </row>
@@ -3163,23 +3153,27 @@
         <v>6</v>
       </c>
       <c r="E68" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F68" s="2">
         <v>4</v>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I68" s="2"/>
-      <c r="J68" s="4"/>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I68" s="3"/>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작은 사선(、) — –로 봄</t>
+        </is>
+      </c>
       <c r="K68" s="2"/>
     </row>
     <row r="69">
@@ -3192,32 +3186,29 @@
         </is>
       </c>
       <c r="C69" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E69" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F69" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I69" s="2"/>
       <c r="J69" s="4"/>
       <c r="K69" s="2"/>
     </row>
@@ -3237,24 +3228,24 @@
         <v>7</v>
       </c>
       <c r="E70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" s="2">
         <v>1</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모</t>
+          <t xml:space="preserve">오</t>
         </is>
       </c>
       <c r="J70" s="4"/>
@@ -3276,22 +3267,26 @@
         <v>7</v>
       </c>
       <c r="E71" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71" s="2">
         <v>1</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I71" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모</t>
+        </is>
+      </c>
       <c r="J71" s="4"/>
       <c r="K71" s="2"/>
     </row>
@@ -3311,26 +3306,22 @@
         <v>7</v>
       </c>
       <c r="E72" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I72" s="2"/>
       <c r="J72" s="4"/>
       <c r="K72" s="2"/>
     </row>
@@ -3350,7 +3341,7 @@
         <v>7</v>
       </c>
       <c r="E73" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F73" s="2">
         <v>2</v>
@@ -3367,7 +3358,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모</t>
+          <t xml:space="preserve">조</t>
         </is>
       </c>
       <c r="J73" s="4"/>
@@ -3389,25 +3380,24 @@
         <v>7</v>
       </c>
       <c r="E74" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F74" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">얼</t>
+          <t xml:space="preserve">모</t>
         </is>
       </c>
       <c r="J74" s="4"/>
@@ -3429,28 +3419,27 @@
         <v>7</v>
       </c>
       <c r="E75" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F75" s="2">
-        <v>3</v>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞|潢</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">뜨을</t>
-        </is>
-      </c>
-      <c r="J75" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I75" s="3"/>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아주 작은 점/선 — 접힌 자국일 수도</t>
+        </is>
+      </c>
       <c r="K75" s="2"/>
     </row>
     <row r="76">
@@ -3469,24 +3458,24 @@
         <v>7</v>
       </c>
       <c r="E76" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F76" s="2">
         <v>3</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">으을</t>
+          <t xml:space="preserve">얼</t>
         </is>
       </c>
       <c r="J76" s="4"/>
@@ -3508,24 +3497,25 @@
         <v>7</v>
       </c>
       <c r="E77" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F77" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㳞
+㴌</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사</t>
+          <t xml:space="preserve">뜨을</t>
         </is>
       </c>
       <c r="J77" s="4"/>
@@ -3547,24 +3537,25 @@
         <v>7</v>
       </c>
       <c r="E78" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F78" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">라앙</t>
+          <t xml:space="preserve">으흘</t>
         </is>
       </c>
       <c r="J78" s="4"/>
@@ -3586,22 +3577,26 @@
         <v>7</v>
       </c>
       <c r="E79" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F79" s="2">
         <v>4</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I79" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
       <c r="J79" s="4"/>
       <c r="K79" s="2"/>
     </row>
@@ -3615,30 +3610,31 @@
         </is>
       </c>
       <c r="C80" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D80" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E80" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F80" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">알</t>
+          <t xml:space="preserve">라앙</t>
         </is>
       </c>
       <c r="J80" s="4"/>
@@ -3654,32 +3650,29 @@
         </is>
       </c>
       <c r="C81" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D81" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E81" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F81" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">깍</t>
-        </is>
-      </c>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="I81" s="2"/>
       <c r="J81" s="4"/>
       <c r="K81" s="2"/>
     </row>
@@ -3699,24 +3692,24 @@
         <v>8</v>
       </c>
       <c r="E82" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F82" s="2">
         <v>1</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">딸</t>
+          <t xml:space="preserve">알</t>
         </is>
       </c>
       <c r="J82" s="4"/>
@@ -3738,105 +3731,101 @@
         <v>8</v>
       </c>
       <c r="E83" s="2">
+        <v>2</v>
+      </c>
+      <c r="F83" s="2">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">깍</t>
+        </is>
+      </c>
+      <c r="J83" s="4"/>
+      <c r="K83" s="2"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2">
+        <v>1</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령.jpg</t>
+        </is>
+      </c>
+      <c r="C84" s="2">
+        <v>8</v>
+      </c>
+      <c r="D84" s="2">
+        <v>8</v>
+      </c>
+      <c r="E84" s="2">
+        <v>3</v>
+      </c>
+      <c r="F84" s="2">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">딸</t>
+        </is>
+      </c>
+      <c r="J84" s="4"/>
+      <c r="K84" s="2"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2">
+        <v>1</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령.jpg</t>
+        </is>
+      </c>
+      <c r="C85" s="2">
+        <v>8</v>
+      </c>
+      <c r="D85" s="2">
+        <v>8</v>
+      </c>
+      <c r="E85" s="2">
         <v>4</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F85" s="2">
         <v>2</v>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–|△</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I83" s="2"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="2"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2">
-        <v>1</v>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령.jpg</t>
-        </is>
-      </c>
-      <c r="C84" s="2">
-        <v>8</v>
-      </c>
-      <c r="D84" s="2">
-        <v>8</v>
-      </c>
-      <c r="E84" s="2">
-        <v>5</v>
-      </c>
-      <c r="F84" s="2">
-        <v>2</v>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">카아</t>
-        </is>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞에 경계 ‹ 표시</t>
-        </is>
-      </c>
-      <c r="K84" s="2"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2">
-        <v>1</v>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령.jpg</t>
-        </is>
-      </c>
-      <c r="C85" s="2">
-        <v>8</v>
-      </c>
-      <c r="D85" s="2">
-        <v>8</v>
-      </c>
-      <c r="E85" s="2">
-        <v>6</v>
-      </c>
-      <c r="F85" s="2">
-        <v>2</v>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아악</t>
-        </is>
-      </c>
+      <c r="I85" s="2"/>
       <c r="J85" s="4"/>
       <c r="K85" s="2"/>
     </row>
@@ -3856,24 +3845,25 @@
         <v>8</v>
       </c>
       <c r="E86" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F86" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">싸아</t>
+          <t xml:space="preserve">카아</t>
         </is>
       </c>
       <c r="J86" s="4"/>
@@ -3895,32 +3885,28 @@
         <v>8</v>
       </c>
       <c r="E87" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F87" s="2">
-        <v>3</v>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우은</t>
-        </is>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|潢</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아악</t>
+        </is>
+      </c>
+      <c r="J87" s="4"/>
       <c r="K87" s="2"/>
     </row>
     <row r="88">
@@ -3939,24 +3925,25 @@
         <v>8</v>
       </c>
       <c r="E88" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F88" s="2">
         <v>3</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사</t>
+          <t xml:space="preserve">싸아</t>
         </is>
       </c>
       <c r="J88" s="4"/>
@@ -3978,31 +3965,28 @@
         <v>8</v>
       </c>
       <c r="E89" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F89" s="2">
-        <v>4</v>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우운</t>
+        </is>
+      </c>
+      <c r="J89" s="4"/>
       <c r="K89" s="2"/>
     </row>
     <row r="90">
@@ -4021,22 +4005,26 @@
         <v>8</v>
       </c>
       <c r="E90" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F90" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I90" s="2"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
       <c r="J90" s="4"/>
       <c r="K90" s="2"/>
     </row>
@@ -4056,22 +4044,26 @@
         <v>8</v>
       </c>
       <c r="E91" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F91" s="2">
         <v>4</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I91" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
       <c r="J91" s="4"/>
       <c r="K91" s="2"/>
     </row>
@@ -4085,38 +4077,29 @@
         </is>
       </c>
       <c r="C92" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D92" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E92" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F92" s="2">
-        <v>1</v>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙|仲</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙
-仲</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I92" s="2"/>
+      <c r="J92" s="4"/>
       <c r="K92" s="2"/>
     </row>
     <row r="93">
@@ -4129,33 +4112,34 @@
         </is>
       </c>
       <c r="C93" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D93" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E93" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F93" s="2">
-        <v>1</v>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">월</t>
-        </is>
-      </c>
-      <c r="J93" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I93" s="3"/>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">– 가 점처럼 짧음</t>
+        </is>
+      </c>
       <c r="K93" s="2"/>
     </row>
     <row r="94">
@@ -4174,22 +4158,27 @@
         <v>9</v>
       </c>
       <c r="E94" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F94" s="2">
         <v>1</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">姑|仲</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I94" s="2"/>
+          <t xml:space="preserve">姑
+仲</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오오</t>
+        </is>
+      </c>
       <c r="J94" s="4"/>
       <c r="K94" s="2"/>
     </row>
@@ -4209,24 +4198,24 @@
         <v>9</v>
       </c>
       <c r="E95" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F95" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼</t>
+          <t xml:space="preserve">월</t>
         </is>
       </c>
       <c r="J95" s="4"/>
@@ -4248,26 +4237,22 @@
         <v>9</v>
       </c>
       <c r="E96" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F96" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">경</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I96" s="2"/>
       <c r="J96" s="4"/>
       <c r="K96" s="2"/>
     </row>
@@ -4287,24 +4272,24 @@
         <v>9</v>
       </c>
       <c r="E97" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F97" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">깊</t>
+          <t xml:space="preserve">삼</t>
         </is>
       </c>
       <c r="J97" s="4"/>
@@ -4326,24 +4311,24 @@
         <v>9</v>
       </c>
       <c r="E98" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F98" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">우우은</t>
+          <t xml:space="preserve">경</t>
         </is>
       </c>
       <c r="J98" s="4"/>
@@ -4365,22 +4350,26 @@
         <v>9</v>
       </c>
       <c r="E99" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F99" s="2">
         <v>3</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="I99" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">깊</t>
+        </is>
+      </c>
       <c r="J99" s="4"/>
       <c r="K99" s="2"/>
     </row>
@@ -4400,24 +4389,25 @@
         <v>9</v>
       </c>
       <c r="E100" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F100" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사</t>
+          <t xml:space="preserve">우우</t>
         </is>
       </c>
       <c r="J100" s="4"/>
@@ -4439,24 +4429,25 @@
         <v>9</v>
       </c>
       <c r="E101" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F101" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">라아</t>
+          <t xml:space="preserve">우운</t>
         </is>
       </c>
       <c r="J101" s="4"/>
@@ -4478,22 +4469,26 @@
         <v>9</v>
       </c>
       <c r="E102" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F102" s="2">
         <v>4</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I102" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
       <c r="J102" s="4"/>
       <c r="K102" s="2"/>
     </row>
@@ -4507,38 +4502,34 @@
         </is>
       </c>
       <c r="C103" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E103" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F103" s="2">
-        <v>1</v>
-      </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙|姑</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙
-姑</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공</t>
-        </is>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라아</t>
+        </is>
+      </c>
+      <c r="J103" s="4"/>
       <c r="K103" s="2"/>
     </row>
     <row r="104">
@@ -4551,30 +4542,31 @@
         </is>
       </c>
       <c r="C104" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D104" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E104" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F104" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">仲
+姑</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼</t>
+          <t xml:space="preserve">앙</t>
         </is>
       </c>
       <c r="J104" s="4"/>
@@ -4596,24 +4588,24 @@
         <v>10</v>
       </c>
       <c r="E105" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F105" s="2">
         <v>1</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">야</t>
+          <t xml:space="preserve">공</t>
         </is>
       </c>
       <c r="J105" s="4"/>
@@ -4635,24 +4627,24 @@
         <v>10</v>
       </c>
       <c r="E106" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F106" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">월</t>
+          <t xml:space="preserve">산</t>
         </is>
       </c>
       <c r="J106" s="4"/>
@@ -4674,24 +4666,24 @@
         <v>10</v>
       </c>
       <c r="E107" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F107" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">달</t>
+          <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="J107" s="4"/>
@@ -4713,25 +4705,24 @@
         <v>10</v>
       </c>
       <c r="E108" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F108" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">밝던</t>
+          <t xml:space="preserve">월</t>
         </is>
       </c>
       <c r="J108" s="4"/>
@@ -4753,26 +4744,22 @@
         <v>10</v>
       </c>
       <c r="E109" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F109" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우은</t>
-        </is>
-      </c>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I109" s="2"/>
       <c r="J109" s="4"/>
       <c r="K109" s="2"/>
     </row>
@@ -4792,24 +4779,24 @@
         <v>10</v>
       </c>
       <c r="E110" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F110" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">밤</t>
+          <t xml:space="preserve">달</t>
         </is>
       </c>
       <c r="J110" s="4"/>
@@ -4831,27 +4818,31 @@
         <v>10</v>
       </c>
       <c r="E111" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F111" s="2">
-        <v>4</v>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에에</t>
-        </is>
-      </c>
-      <c r="J111" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밝</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 밝?(바+ㄺ 모양)</t>
+        </is>
+      </c>
       <c r="K111" s="2"/>
     </row>
     <row r="112">
@@ -4870,36 +4861,151 @@
         <v>10</v>
       </c>
       <c r="E112" s="2">
+        <v>9</v>
+      </c>
+      <c r="F112" s="2">
+        <v>3</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|無</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우운</t>
+        </is>
+      </c>
+      <c r="J112" s="4"/>
+      <c r="K112" s="2"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2">
+        <v>1</v>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령.jpg</t>
+        </is>
+      </c>
+      <c r="C113" s="2">
+        <v>10</v>
+      </c>
+      <c r="D113" s="2">
+        <v>10</v>
+      </c>
+      <c r="E113" s="2">
+        <v>10</v>
+      </c>
+      <c r="F113" s="2">
+        <v>4</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밤</t>
+        </is>
+      </c>
+      <c r="J113" s="4"/>
+      <c r="K113" s="2"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2">
+        <v>1</v>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령.jpg</t>
+        </is>
+      </c>
+      <c r="C114" s="2">
+        <v>10</v>
+      </c>
+      <c r="D114" s="2">
+        <v>10</v>
+      </c>
+      <c r="E114" s="2">
+        <v>11</v>
+      </c>
+      <c r="F114" s="2">
+        <v>4</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에에</t>
+        </is>
+      </c>
+      <c r="J114" s="4"/>
+      <c r="K114" s="2"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2">
+        <v>1</v>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령.jpg</t>
+        </is>
+      </c>
+      <c r="C115" s="2">
+        <v>10</v>
+      </c>
+      <c r="D115" s="2">
+        <v>10</v>
+      </c>
+      <c r="E115" s="2">
         <v>12</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F115" s="2">
         <v>4</v>
       </c>
-      <c r="G112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
-      <c r="K112" s="2"/>
+姑</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에이</t>
+        </is>
+      </c>
+      <c r="J115" s="4"/>
+      <c r="K115" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K112"/>
+  <autoFilter ref="A1:K115"/>
 </worksheet>
 </file>
 
@@ -4932,7 +5038,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4959,688 +5065,720 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙
-姑</t>
-        </is>
-      </c>
-      <c r="C3" s="29" t="inlineStr">
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">공</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙
+          <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오
+오</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">알</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="M3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">얼</t>
+        </is>
+      </c>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="O3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–湳</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+      <c r="R3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="T3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+仲</t>
+        </is>
+      </c>
+      <c r="U3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+아</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52.21" customHeight="1">
+      <c r="A4" s="0"/>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">월</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">깍</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="O4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="Q4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">알</t>
-        </is>
-      </c>
-      <c r="H3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="I3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오</t>
-        </is>
-      </c>
-      <c r="J3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민</t>
-        </is>
-      </c>
-      <c r="L3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="M3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">얼</t>
-        </is>
-      </c>
-      <c r="N3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="O3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
-      <c r="P3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙
-仲</t>
-        </is>
-      </c>
-      <c r="S3" s="29"/>
-      <c r="T3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="U3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
-      <c r="A4" s="0"/>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삼</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">월</t>
-        </is>
-      </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">깍</t>
-        </is>
-      </c>
-      <c r="H4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">모</t>
-        </is>
-      </c>
-      <c r="J4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="L4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="N4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="O4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="P4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="Q4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="R4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="S4" s="32" t="inlineStr">
+      <c r="S4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="T4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U4" s="31" t="inlineStr">
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="55.19" customHeight="1">
+    <row r="5" ht="52.21" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="inlineStr">
+      <c r="E5" s="24"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">딸</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="33"/>
-      <c r="J5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K5" s="33" t="inlineStr">
+      <c r="I5" s="24"/>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L5" s="23" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="M5" s="33" t="inlineStr">
+      <c r="M5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="O5" s="33" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="O5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P5" s="23" t="inlineStr">
+      <c r="P5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="23" t="inlineStr">
+      <c r="Q5" s="26"/>
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="S5" s="33"/>
-      <c r="T5" s="23"/>
-      <c r="U5" s="33"/>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
+      <c r="S5" s="24"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="24"/>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="B6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="30" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">조</t>
         </is>
       </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="30"/>
-      <c r="L6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="M6" s="30" t="inlineStr">
+      <c r="K6" s="22"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="N6" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="O6" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">란</t>
+        </is>
+      </c>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="N6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="O6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">란</t>
-        </is>
-      </c>
-      <c r="P6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="Q6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
-      <c r="R6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S6" s="30" t="inlineStr">
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="S6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="T6" s="23"/>
-      <c r="U6" s="30"/>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
+      <c r="T6" s="21"/>
+      <c r="U6" s="22"/>
+    </row>
+    <row r="7" ht="52.21" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="G7" s="32" t="inlineStr">
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">카
 아</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I7" s="31" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="K7" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조</t>
-        </is>
-      </c>
-      <c r="L7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="M7" s="31" t="inlineStr">
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">도
 오</t>
         </is>
       </c>
-      <c r="N7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="M7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도
+오</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="O7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">것</t>
+        </is>
+      </c>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="Q7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
+      <c r="R7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="S7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지</t>
+        </is>
+      </c>
+      <c r="T7" s="21"/>
+      <c r="U7" s="23"/>
+    </row>
+    <row r="8" ht="52.21" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">것</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="Q7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="R7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="S7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">지</t>
-        </is>
-      </c>
-      <c r="T7" s="23"/>
-      <c r="U7" s="31"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
-      <c r="A8" s="0"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="G8" s="33" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 악</t>
         </is>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="K8" s="33"/>
-      <c r="L8" s="23" t="inlineStr">
+      <c r="H8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I8" s="26"/>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">호
+오</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="M8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오
+호</t>
+        </is>
+      </c>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="O8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오
-오</t>
-        </is>
-      </c>
-      <c r="N8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="O8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="S8" s="33" t="inlineStr">
+      <c r="S8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="T8" s="23"/>
-      <c r="U8" s="33"/>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
+      <c r="T8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U8" s="26"/>
+    </row>
+    <row r="9" ht="52.21" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">깊</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="G9" s="30" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">싸
 아</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I9" s="30" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="K9" s="30" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">소
 은</t>
         </is>
       </c>
-      <c r="L9" s="23" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="M9" s="30" t="inlineStr">
+㴌</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">모
 호</t>
         </is>
       </c>
-      <c r="N9" s="23" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="O9" s="30" t="inlineStr">
+㴌</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="P9" s="23" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="Q9" s="30" t="inlineStr">
+湳</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="R9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="S9" s="30" t="inlineStr">
+      <c r="R9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="S9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
       <c r="T9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U9" s="29" t="inlineStr">
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="55.19" customHeight="1">
+    <row r="10" ht="52.21" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밝</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우
+우</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우
+운</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">밝
-던</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우
-우
-은</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="G10" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우
-은</t>
-        </is>
-      </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I10" s="31" t="inlineStr">
+㴌</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">뜨
 을</t>
@@ -5649,42 +5787,42 @@
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="K10" s="32" t="inlineStr">
+姑</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">으
 은</t>
         </is>
       </c>
-      <c r="L10" s="23" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M10" s="31" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="N10" s="23" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O10" s="31" t="inlineStr">
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">엇</t>
         </is>
       </c>
-      <c r="P10" s="23" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="Q10" s="31" t="inlineStr">
+㴌</t>
+        </is>
+      </c>
+      <c r="Q10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -5692,375 +5830,403 @@
       <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="S10" s="32" t="inlineStr">
+姑</t>
+        </is>
+      </c>
+      <c r="S10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="T10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="U10" s="31"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
+      <c r="T10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="U10" s="23"/>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">우
-은</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="23" t="inlineStr">
+운</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우
+운</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G11" s="33" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="I11" s="33" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">으
-을</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="inlineStr">
+흘</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K11" s="33" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="L11" s="23" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="M11" s="33" t="inlineStr">
+      <c r="M11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">흘</t>
         </is>
       </c>
-      <c r="N11" s="23" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O11" s="33"/>
-      <c r="P11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="Q11" s="33" t="inlineStr">
+      <c r="O11" s="24"/>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="Q11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 러</t>
         </is>
       </c>
-      <c r="R11" s="23" t="inlineStr">
+      <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S11" s="33" t="inlineStr">
+      <c r="S11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="T11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="U11" s="33"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
+      <c r="T11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="U11" s="24"/>
+    </row>
+    <row r="12" ht="52.21" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밤</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">밤</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="30" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니</t>
+        </is>
+      </c>
+      <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="K12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="L12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
-      <c r="N12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O12" s="30" t="inlineStr">
+      <c r="S12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라</t>
+        </is>
+      </c>
+      <c r="T12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="Q12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니</t>
-        </is>
-      </c>
-      <c r="R12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="S12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">라</t>
-        </is>
-      </c>
-      <c r="T12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
+    </row>
+    <row r="13" ht="52.21" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">에
 에</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="E13" s="31" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">라
 아</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="31"/>
-      <c r="H13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="I13" s="31" t="inlineStr">
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">라
 앙</t>
         </is>
       </c>
-      <c r="J13" s="23" t="inlineStr">
+      <c r="J13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="M13" s="31" t="inlineStr">
+      <c r="K13" s="28"/>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">라
 앙</t>
         </is>
       </c>
-      <c r="N13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="P13" s="23" t="inlineStr">
+      <c r="N13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O13" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">냐</t>
+        </is>
+      </c>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="23" t="inlineStr">
+      <c r="Q13" s="23"/>
+      <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S13" s="31"/>
-      <c r="T13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="U13" s="31"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
+      <c r="S13" s="23"/>
+      <c r="T13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="U13" s="23"/>
+    </row>
+    <row r="14" ht="52.21" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G14" s="33"/>
-      <c r="H14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I14" s="33"/>
-      <c r="J14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K14" s="33"/>
-      <c r="L14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M14" s="33"/>
-      <c r="N14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="O14" s="33"/>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S14" s="33"/>
-      <c r="T14" s="23" t="inlineStr">
+姑</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+이</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="U14" s="33"/>
+姑</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앙</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="I14" s="24"/>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="K14" s="24"/>
+      <c r="L14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="M14" s="26"/>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="O14" s="24"/>
+      <c r="P14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="S14" s="24"/>
+      <c r="T14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="U14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
